--- a/LoteriasExcel/MegaSena_edt.xlsx
+++ b/LoteriasExcel/MegaSena_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7168E5F9-FD66-4B2D-851F-E0B1C8DF64D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1DBABD9-586E-4498-8A8D-4D6071A027C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="78675" yWindow="615" windowWidth="17280" windowHeight="18765" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="58095" yWindow="3090" windowWidth="21585" windowHeight="17475" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="MEGA SENA" sheetId="4" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Concurso</t>
   </si>
@@ -55,9 +55,6 @@
   </si>
   <si>
     <t>Bola6</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -112,14 +109,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -440,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA4E33BD-754C-4CC3-9530-49E6C4C5E994}">
-  <dimension ref="A1:G429"/>
+  <dimension ref="A1:G432"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.07421875" customWidth="1"/>
@@ -10136,181 +10130,253 @@
       <c r="A422">
         <v>2965</v>
       </c>
-      <c r="B422" s="4">
+      <c r="B422">
         <v>1</v>
       </c>
-      <c r="C422" s="4">
+      <c r="C422">
         <v>20</v>
       </c>
-      <c r="D422" s="4">
+      <c r="D422">
         <v>22</v>
       </c>
-      <c r="E422" s="4">
+      <c r="E422">
         <v>23</v>
       </c>
-      <c r="F422" s="4">
+      <c r="F422">
         <v>35</v>
       </c>
-      <c r="G422" s="4">
+      <c r="G422">
         <v>57</v>
       </c>
     </row>
     <row r="423" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A423" s="2">
+      <c r="A423">
         <v>2966</v>
       </c>
-      <c r="B423" s="4">
+      <c r="B423">
         <v>6</v>
       </c>
-      <c r="C423" s="4">
+      <c r="C423">
         <v>7</v>
       </c>
-      <c r="D423" s="4">
+      <c r="D423">
         <v>9</v>
       </c>
-      <c r="E423" s="4">
+      <c r="E423">
         <v>43</v>
       </c>
-      <c r="F423" s="4">
+      <c r="F423">
         <v>44</v>
       </c>
-      <c r="G423" s="4">
+      <c r="G423">
         <v>53</v>
       </c>
     </row>
     <row r="424" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A424" s="2">
+      <c r="A424">
         <v>2967</v>
       </c>
-      <c r="B424" s="4">
+      <c r="B424">
         <v>1</v>
       </c>
-      <c r="C424" s="4">
+      <c r="C424">
         <v>6</v>
       </c>
-      <c r="D424" s="4">
+      <c r="D424">
         <v>38</v>
       </c>
-      <c r="E424" s="4">
+      <c r="E424">
         <v>47</v>
       </c>
-      <c r="F424" s="4">
+      <c r="F424">
         <v>56</v>
       </c>
-      <c r="G424" s="4">
+      <c r="G424">
         <v>60</v>
       </c>
     </row>
     <row r="425" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A425" s="2">
+      <c r="A425">
         <v>2968</v>
       </c>
-      <c r="B425" s="4">
+      <c r="B425">
         <v>10</v>
       </c>
-      <c r="C425" s="4">
+      <c r="C425">
         <v>11</v>
       </c>
-      <c r="D425" s="4">
+      <c r="D425">
         <v>22</v>
       </c>
-      <c r="E425" s="4">
+      <c r="E425">
         <v>26</v>
       </c>
-      <c r="F425" s="4">
+      <c r="F425">
         <v>36</v>
       </c>
-      <c r="G425" s="4">
+      <c r="G425">
         <v>46</v>
       </c>
     </row>
     <row r="426" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A426" s="2">
+      <c r="A426">
         <v>2969</v>
       </c>
-      <c r="B426" s="4">
+      <c r="B426">
         <v>1</v>
       </c>
-      <c r="C426" s="4">
+      <c r="C426">
         <v>2</v>
       </c>
-      <c r="D426" s="4">
+      <c r="D426">
         <v>5</v>
       </c>
-      <c r="E426" s="4">
+      <c r="E426">
         <v>14</v>
       </c>
-      <c r="F426" s="4">
+      <c r="F426">
         <v>18</v>
       </c>
-      <c r="G426" s="4">
+      <c r="G426">
         <v>32</v>
       </c>
     </row>
     <row r="427" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A427" s="2">
+      <c r="A427">
         <v>2970</v>
       </c>
-      <c r="B427" s="4">
+      <c r="B427">
         <v>22</v>
       </c>
-      <c r="C427" s="4">
+      <c r="C427">
         <v>32</v>
       </c>
-      <c r="D427" s="4">
+      <c r="D427">
         <v>37</v>
       </c>
-      <c r="E427" s="4">
+      <c r="E427">
         <v>41</v>
       </c>
-      <c r="F427" s="4">
+      <c r="F427">
         <v>42</v>
       </c>
-      <c r="G427" s="4">
+      <c r="G427">
         <v>59</v>
       </c>
     </row>
     <row r="428" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A428" s="2">
+      <c r="A428">
         <v>2971</v>
       </c>
-      <c r="B428" s="4">
+      <c r="B428">
         <v>1</v>
       </c>
-      <c r="C428" s="4">
+      <c r="C428">
         <v>27</v>
       </c>
-      <c r="D428" s="4">
+      <c r="D428">
         <v>39</v>
       </c>
-      <c r="E428" s="4">
+      <c r="E428">
         <v>40</v>
       </c>
-      <c r="F428" s="4">
+      <c r="F428">
         <v>46</v>
       </c>
-      <c r="G428" s="4">
+      <c r="G428">
         <v>56</v>
       </c>
     </row>
     <row r="429" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="B429" s="3" t="s">
+      <c r="A429">
+        <v>2972</v>
+      </c>
+      <c r="B429">
+        <v>9</v>
+      </c>
+      <c r="C429">
+        <v>10</v>
+      </c>
+      <c r="D429">
+        <v>15</v>
+      </c>
+      <c r="E429">
+        <v>46</v>
+      </c>
+      <c r="F429">
+        <v>49</v>
+      </c>
+      <c r="G429">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="430" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A430">
+        <v>2973</v>
+      </c>
+      <c r="B430">
+        <v>16</v>
+      </c>
+      <c r="C430">
+        <v>24</v>
+      </c>
+      <c r="D430">
+        <v>27</v>
+      </c>
+      <c r="E430">
+        <v>31</v>
+      </c>
+      <c r="F430">
+        <v>45</v>
+      </c>
+      <c r="G430">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="431" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A431">
+        <v>2974</v>
+      </c>
+      <c r="B431">
+        <v>3</v>
+      </c>
+      <c r="C431">
+        <v>10</v>
+      </c>
+      <c r="D431">
+        <v>12</v>
+      </c>
+      <c r="E431">
+        <v>19</v>
+      </c>
+      <c r="F431">
+        <v>37</v>
+      </c>
+      <c r="G431">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="432" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A432">
+        <v>2975</v>
+      </c>
+      <c r="B432">
         <v>7</v>
       </c>
-      <c r="C429" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D429" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E429" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F429" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G429" s="3" t="s">
-        <v>7</v>
+      <c r="C432">
+        <v>10</v>
+      </c>
+      <c r="D432">
+        <v>17</v>
+      </c>
+      <c r="E432">
+        <v>35</v>
+      </c>
+      <c r="F432">
+        <v>44</v>
+      </c>
+      <c r="G432">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -10488,6 +10554,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
@@ -10495,15 +10570,6 @@
     <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-31T04:01:53+00:00</AtualizadoPeloTimerJobEm>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10527,6 +10593,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64615F65-CF13-4100-B135-FA0CB5E1C951}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -10535,12 +10609,4 @@
     <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/LoteriasExcel/MegaSena_edt.xlsx
+++ b/LoteriasExcel/MegaSena_edt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1DBABD9-586E-4498-8A8D-4D6071A027C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66B927D0-3D03-46BC-9874-89B2CDA9EED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="58095" yWindow="3090" windowWidth="21585" windowHeight="17475" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="MEGA SENA" sheetId="4" r:id="rId1"/>
@@ -434,16 +434,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA4E33BD-754C-4CC3-9530-49E6C4C5E994}">
-  <dimension ref="A1:G432"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:G449"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="10.07421875" customWidth="1"/>
-    <col min="8" max="8" width="16.4609375" customWidth="1"/>
-    <col min="9" max="9" width="16.3046875" customWidth="1"/>
+    <col min="1" max="1" width="10.06640625" customWidth="1"/>
+    <col min="8" max="8" width="16.46484375" customWidth="1"/>
+    <col min="9" max="9" width="16.33203125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -466,7 +466,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>2545</v>
       </c>
@@ -489,7 +489,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>2546</v>
       </c>
@@ -512,7 +512,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>2547</v>
       </c>
@@ -535,7 +535,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>2548</v>
       </c>
@@ -558,7 +558,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>2549</v>
       </c>
@@ -581,7 +581,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>2550</v>
       </c>
@@ -604,7 +604,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>2551</v>
       </c>
@@ -627,7 +627,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>2552</v>
       </c>
@@ -650,7 +650,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>2553</v>
       </c>
@@ -673,7 +673,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>2554</v>
       </c>
@@ -696,7 +696,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>2555</v>
       </c>
@@ -719,7 +719,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>2556</v>
       </c>
@@ -742,7 +742,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>2557</v>
       </c>
@@ -765,7 +765,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>2558</v>
       </c>
@@ -788,7 +788,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>2559</v>
       </c>
@@ -811,7 +811,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>2560</v>
       </c>
@@ -834,7 +834,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>2561</v>
       </c>
@@ -857,7 +857,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>2562</v>
       </c>
@@ -880,7 +880,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>2563</v>
       </c>
@@ -903,7 +903,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>2564</v>
       </c>
@@ -926,7 +926,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>2565</v>
       </c>
@@ -949,7 +949,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>2566</v>
       </c>
@@ -972,7 +972,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>2567</v>
       </c>
@@ -995,7 +995,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>2568</v>
       </c>
@@ -1018,7 +1018,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>2569</v>
       </c>
@@ -1041,7 +1041,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>2570</v>
       </c>
@@ -1064,7 +1064,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>2571</v>
       </c>
@@ -1087,7 +1087,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>2572</v>
       </c>
@@ -1110,7 +1110,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>2573</v>
       </c>
@@ -1133,7 +1133,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>2574</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>2575</v>
       </c>
@@ -1179,7 +1179,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>2576</v>
       </c>
@@ -1202,7 +1202,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>2577</v>
       </c>
@@ -1225,7 +1225,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>2578</v>
       </c>
@@ -1248,7 +1248,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>2579</v>
       </c>
@@ -1271,7 +1271,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>2580</v>
       </c>
@@ -1294,7 +1294,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>2581</v>
       </c>
@@ -1317,7 +1317,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>2582</v>
       </c>
@@ -1340,7 +1340,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>2583</v>
       </c>
@@ -1363,7 +1363,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>2584</v>
       </c>
@@ -1386,7 +1386,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>2585</v>
       </c>
@@ -1409,7 +1409,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>2586</v>
       </c>
@@ -1432,7 +1432,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>2587</v>
       </c>
@@ -1455,7 +1455,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>2588</v>
       </c>
@@ -1478,7 +1478,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>2589</v>
       </c>
@@ -1501,7 +1501,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>2590</v>
       </c>
@@ -1524,7 +1524,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>2591</v>
       </c>
@@ -1547,7 +1547,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A49">
         <v>2592</v>
       </c>
@@ -1570,7 +1570,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A50">
         <v>2593</v>
       </c>
@@ -1593,7 +1593,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A51">
         <v>2594</v>
       </c>
@@ -1616,7 +1616,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>2595</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>2596</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A54">
         <v>2597</v>
       </c>
@@ -1685,7 +1685,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>2598</v>
       </c>
@@ -1708,7 +1708,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A56">
         <v>2599</v>
       </c>
@@ -1731,7 +1731,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A57">
         <v>2600</v>
       </c>
@@ -1754,7 +1754,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A58">
         <v>2601</v>
       </c>
@@ -1777,7 +1777,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A59">
         <v>2602</v>
       </c>
@@ -1800,7 +1800,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A60">
         <v>2603</v>
       </c>
@@ -1823,7 +1823,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A61">
         <v>2604</v>
       </c>
@@ -1846,7 +1846,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A62">
         <v>2605</v>
       </c>
@@ -1869,7 +1869,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A63">
         <v>2606</v>
       </c>
@@ -1892,7 +1892,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A64">
         <v>2607</v>
       </c>
@@ -1915,7 +1915,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A65">
         <v>2608</v>
       </c>
@@ -1938,7 +1938,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A66">
         <v>2609</v>
       </c>
@@ -1961,7 +1961,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A67">
         <v>2610</v>
       </c>
@@ -1984,7 +1984,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A68">
         <v>2611</v>
       </c>
@@ -2007,7 +2007,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A69">
         <v>2612</v>
       </c>
@@ -2030,7 +2030,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A70">
         <v>2613</v>
       </c>
@@ -2053,7 +2053,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A71">
         <v>2614</v>
       </c>
@@ -2076,7 +2076,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A72">
         <v>2615</v>
       </c>
@@ -2099,7 +2099,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A73">
         <v>2616</v>
       </c>
@@ -2122,7 +2122,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A74">
         <v>2617</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A75">
         <v>2618</v>
       </c>
@@ -2168,7 +2168,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A76">
         <v>2619</v>
       </c>
@@ -2191,7 +2191,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A77">
         <v>2620</v>
       </c>
@@ -2214,7 +2214,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A78">
         <v>2621</v>
       </c>
@@ -2237,7 +2237,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A79">
         <v>2622</v>
       </c>
@@ -2260,7 +2260,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A80">
         <v>2623</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A81">
         <v>2624</v>
       </c>
@@ -2306,7 +2306,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A82">
         <v>2625</v>
       </c>
@@ -2329,7 +2329,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A83">
         <v>2626</v>
       </c>
@@ -2352,7 +2352,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A84">
         <v>2627</v>
       </c>
@@ -2375,7 +2375,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A85">
         <v>2628</v>
       </c>
@@ -2398,7 +2398,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A86">
         <v>2629</v>
       </c>
@@ -2421,7 +2421,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A87">
         <v>2630</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A88">
         <v>2631</v>
       </c>
@@ -2467,7 +2467,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A89">
         <v>2632</v>
       </c>
@@ -2490,7 +2490,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A90">
         <v>2633</v>
       </c>
@@ -2513,7 +2513,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A91">
         <v>2634</v>
       </c>
@@ -2536,7 +2536,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A92">
         <v>2635</v>
       </c>
@@ -2559,7 +2559,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A93">
         <v>2636</v>
       </c>
@@ -2582,7 +2582,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A94">
         <v>2637</v>
       </c>
@@ -2605,7 +2605,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A95">
         <v>2638</v>
       </c>
@@ -2628,7 +2628,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A96">
         <v>2639</v>
       </c>
@@ -2651,7 +2651,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A97">
         <v>2640</v>
       </c>
@@ -2674,7 +2674,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A98">
         <v>2641</v>
       </c>
@@ -2697,7 +2697,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A99">
         <v>2642</v>
       </c>
@@ -2720,7 +2720,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A100">
         <v>2643</v>
       </c>
@@ -2743,7 +2743,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A101">
         <v>2644</v>
       </c>
@@ -2766,7 +2766,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A102">
         <v>2645</v>
       </c>
@@ -2789,7 +2789,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A103">
         <v>2646</v>
       </c>
@@ -2812,7 +2812,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A104">
         <v>2647</v>
       </c>
@@ -2835,7 +2835,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A105">
         <v>2648</v>
       </c>
@@ -2858,7 +2858,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A106">
         <v>2649</v>
       </c>
@@ -2881,7 +2881,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A107">
         <v>2650</v>
       </c>
@@ -2904,7 +2904,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A108">
         <v>2651</v>
       </c>
@@ -2927,7 +2927,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A109">
         <v>2652</v>
       </c>
@@ -2950,7 +2950,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A110">
         <v>2653</v>
       </c>
@@ -2973,7 +2973,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A111">
         <v>2654</v>
       </c>
@@ -2996,7 +2996,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A112">
         <v>2655</v>
       </c>
@@ -3019,7 +3019,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A113">
         <v>2656</v>
       </c>
@@ -3042,7 +3042,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A114">
         <v>2657</v>
       </c>
@@ -3065,7 +3065,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A115">
         <v>2658</v>
       </c>
@@ -3088,7 +3088,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A116">
         <v>2659</v>
       </c>
@@ -3111,7 +3111,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A117">
         <v>2660</v>
       </c>
@@ -3134,7 +3134,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A118">
         <v>2661</v>
       </c>
@@ -3157,7 +3157,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A119">
         <v>2662</v>
       </c>
@@ -3180,7 +3180,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A120">
         <v>2663</v>
       </c>
@@ -3203,7 +3203,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A121">
         <v>2664</v>
       </c>
@@ -3226,7 +3226,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A122">
         <v>2665</v>
       </c>
@@ -3249,7 +3249,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A123">
         <v>2666</v>
       </c>
@@ -3272,7 +3272,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A124">
         <v>2667</v>
       </c>
@@ -3295,7 +3295,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A125">
         <v>2668</v>
       </c>
@@ -3318,7 +3318,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A126">
         <v>2669</v>
       </c>
@@ -3341,7 +3341,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A127">
         <v>2670</v>
       </c>
@@ -3364,7 +3364,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A128">
         <v>2671</v>
       </c>
@@ -3387,7 +3387,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A129">
         <v>2672</v>
       </c>
@@ -3410,7 +3410,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A130">
         <v>2673</v>
       </c>
@@ -3433,7 +3433,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A131">
         <v>2674</v>
       </c>
@@ -3456,7 +3456,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A132">
         <v>2675</v>
       </c>
@@ -3479,7 +3479,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A133">
         <v>2676</v>
       </c>
@@ -3502,7 +3502,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A134">
         <v>2677</v>
       </c>
@@ -3525,7 +3525,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A135">
         <v>2678</v>
       </c>
@@ -3548,7 +3548,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A136">
         <v>2679</v>
       </c>
@@ -3571,7 +3571,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A137">
         <v>2680</v>
       </c>
@@ -3594,7 +3594,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A138">
         <v>2681</v>
       </c>
@@ -3617,7 +3617,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A139">
         <v>2682</v>
       </c>
@@ -3640,7 +3640,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A140">
         <v>2683</v>
       </c>
@@ -3663,7 +3663,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A141">
         <v>2684</v>
       </c>
@@ -3686,7 +3686,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A142">
         <v>2685</v>
       </c>
@@ -3709,7 +3709,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A143">
         <v>2686</v>
       </c>
@@ -3732,7 +3732,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A144">
         <v>2687</v>
       </c>
@@ -3755,7 +3755,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A145">
         <v>2688</v>
       </c>
@@ -3778,7 +3778,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A146">
         <v>2689</v>
       </c>
@@ -3801,7 +3801,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A147">
         <v>2690</v>
       </c>
@@ -3824,7 +3824,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A148">
         <v>2691</v>
       </c>
@@ -3847,7 +3847,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A149">
         <v>2692</v>
       </c>
@@ -3870,7 +3870,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A150">
         <v>2693</v>
       </c>
@@ -3893,7 +3893,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A151">
         <v>2694</v>
       </c>
@@ -3916,7 +3916,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A152">
         <v>2695</v>
       </c>
@@ -3939,7 +3939,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A153">
         <v>2696</v>
       </c>
@@ -3962,7 +3962,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A154">
         <v>2697</v>
       </c>
@@ -3985,7 +3985,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A155">
         <v>2698</v>
       </c>
@@ -4008,7 +4008,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A156">
         <v>2699</v>
       </c>
@@ -4031,7 +4031,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A157">
         <v>2700</v>
       </c>
@@ -4054,7 +4054,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A158">
         <v>2701</v>
       </c>
@@ -4077,7 +4077,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A159">
         <v>2702</v>
       </c>
@@ -4100,7 +4100,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A160">
         <v>2703</v>
       </c>
@@ -4123,7 +4123,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A161">
         <v>2704</v>
       </c>
@@ -4146,7 +4146,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A162">
         <v>2705</v>
       </c>
@@ -4169,7 +4169,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A163">
         <v>2706</v>
       </c>
@@ -4192,7 +4192,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A164">
         <v>2707</v>
       </c>
@@ -4215,7 +4215,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A165">
         <v>2708</v>
       </c>
@@ -4238,7 +4238,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A166">
         <v>2709</v>
       </c>
@@ -4261,7 +4261,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A167">
         <v>2710</v>
       </c>
@@ -4284,7 +4284,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A168">
         <v>2711</v>
       </c>
@@ -4307,7 +4307,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A169">
         <v>2712</v>
       </c>
@@ -4330,7 +4330,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A170">
         <v>2713</v>
       </c>
@@ -4353,7 +4353,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A171">
         <v>2714</v>
       </c>
@@ -4376,7 +4376,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A172">
         <v>2715</v>
       </c>
@@ -4399,7 +4399,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A173">
         <v>2716</v>
       </c>
@@ -4422,7 +4422,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A174">
         <v>2717</v>
       </c>
@@ -4445,7 +4445,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A175">
         <v>2718</v>
       </c>
@@ -4468,7 +4468,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A176">
         <v>2719</v>
       </c>
@@ -4491,7 +4491,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A177">
         <v>2720</v>
       </c>
@@ -4514,7 +4514,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A178">
         <v>2721</v>
       </c>
@@ -4537,7 +4537,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A179">
         <v>2722</v>
       </c>
@@ -4560,7 +4560,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A180">
         <v>2723</v>
       </c>
@@ -4583,7 +4583,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A181">
         <v>2724</v>
       </c>
@@ -4606,7 +4606,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A182">
         <v>2725</v>
       </c>
@@ -4629,7 +4629,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A183">
         <v>2726</v>
       </c>
@@ -4652,7 +4652,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A184">
         <v>2727</v>
       </c>
@@ -4675,7 +4675,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A185">
         <v>2728</v>
       </c>
@@ -4698,7 +4698,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A186">
         <v>2729</v>
       </c>
@@ -4721,7 +4721,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A187">
         <v>2730</v>
       </c>
@@ -4744,7 +4744,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A188">
         <v>2731</v>
       </c>
@@ -4767,7 +4767,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A189">
         <v>2732</v>
       </c>
@@ -4790,7 +4790,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A190">
         <v>2733</v>
       </c>
@@ -4813,7 +4813,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A191">
         <v>2734</v>
       </c>
@@ -4836,7 +4836,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A192">
         <v>2735</v>
       </c>
@@ -4859,7 +4859,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A193">
         <v>2736</v>
       </c>
@@ -4882,7 +4882,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A194">
         <v>2737</v>
       </c>
@@ -4905,7 +4905,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A195">
         <v>2738</v>
       </c>
@@ -4928,7 +4928,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A196">
         <v>2739</v>
       </c>
@@ -4951,7 +4951,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A197">
         <v>2740</v>
       </c>
@@ -4974,7 +4974,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A198">
         <v>2741</v>
       </c>
@@ -4997,7 +4997,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A199">
         <v>2742</v>
       </c>
@@ -5020,7 +5020,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A200">
         <v>2743</v>
       </c>
@@ -5043,7 +5043,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A201">
         <v>2744</v>
       </c>
@@ -5066,7 +5066,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A202">
         <v>2745</v>
       </c>
@@ -5089,7 +5089,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A203">
         <v>2746</v>
       </c>
@@ -5112,7 +5112,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A204">
         <v>2747</v>
       </c>
@@ -5135,7 +5135,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A205">
         <v>2748</v>
       </c>
@@ -5158,7 +5158,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A206">
         <v>2749</v>
       </c>
@@ -5181,7 +5181,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A207">
         <v>2750</v>
       </c>
@@ -5204,7 +5204,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A208">
         <v>2751</v>
       </c>
@@ -5227,7 +5227,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A209">
         <v>2752</v>
       </c>
@@ -5250,7 +5250,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A210">
         <v>2753</v>
       </c>
@@ -5273,7 +5273,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A211">
         <v>2754</v>
       </c>
@@ -5296,7 +5296,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A212">
         <v>2755</v>
       </c>
@@ -5319,7 +5319,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A213">
         <v>2756</v>
       </c>
@@ -5342,7 +5342,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A214">
         <v>2757</v>
       </c>
@@ -5365,7 +5365,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A215">
         <v>2758</v>
       </c>
@@ -5388,7 +5388,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A216">
         <v>2759</v>
       </c>
@@ -5411,7 +5411,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A217">
         <v>2760</v>
       </c>
@@ -5434,7 +5434,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A218">
         <v>2761</v>
       </c>
@@ -5457,7 +5457,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A219">
         <v>2762</v>
       </c>
@@ -5480,7 +5480,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A220">
         <v>2763</v>
       </c>
@@ -5503,7 +5503,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A221">
         <v>2764</v>
       </c>
@@ -5526,7 +5526,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A222">
         <v>2765</v>
       </c>
@@ -5549,7 +5549,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A223">
         <v>2766</v>
       </c>
@@ -5572,7 +5572,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A224">
         <v>2767</v>
       </c>
@@ -5595,7 +5595,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A225">
         <v>2768</v>
       </c>
@@ -5618,7 +5618,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A226">
         <v>2769</v>
       </c>
@@ -5641,7 +5641,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A227">
         <v>2770</v>
       </c>
@@ -5664,7 +5664,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A228">
         <v>2771</v>
       </c>
@@ -5687,7 +5687,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A229">
         <v>2772</v>
       </c>
@@ -5710,7 +5710,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A230">
         <v>2773</v>
       </c>
@@ -5733,7 +5733,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A231">
         <v>2774</v>
       </c>
@@ -5756,7 +5756,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A232">
         <v>2775</v>
       </c>
@@ -5779,7 +5779,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A233">
         <v>2776</v>
       </c>
@@ -5802,7 +5802,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A234">
         <v>2777</v>
       </c>
@@ -5825,7 +5825,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A235">
         <v>2778</v>
       </c>
@@ -5848,7 +5848,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A236">
         <v>2779</v>
       </c>
@@ -5871,7 +5871,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A237">
         <v>2780</v>
       </c>
@@ -5894,7 +5894,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A238">
         <v>2781</v>
       </c>
@@ -5917,7 +5917,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A239">
         <v>2782</v>
       </c>
@@ -5940,7 +5940,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A240">
         <v>2783</v>
       </c>
@@ -5963,7 +5963,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A241">
         <v>2784</v>
       </c>
@@ -5986,7 +5986,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A242">
         <v>2785</v>
       </c>
@@ -6009,7 +6009,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A243">
         <v>2786</v>
       </c>
@@ -6032,7 +6032,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A244">
         <v>2787</v>
       </c>
@@ -6055,7 +6055,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A245">
         <v>2788</v>
       </c>
@@ -6078,7 +6078,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A246">
         <v>2789</v>
       </c>
@@ -6101,7 +6101,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A247">
         <v>2790</v>
       </c>
@@ -6124,7 +6124,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A248">
         <v>2791</v>
       </c>
@@ -6147,7 +6147,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A249">
         <v>2792</v>
       </c>
@@ -6170,7 +6170,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A250">
         <v>2793</v>
       </c>
@@ -6193,7 +6193,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A251">
         <v>2794</v>
       </c>
@@ -6216,7 +6216,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A252">
         <v>2795</v>
       </c>
@@ -6239,7 +6239,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A253">
         <v>2796</v>
       </c>
@@ -6262,7 +6262,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A254">
         <v>2797</v>
       </c>
@@ -6285,7 +6285,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A255">
         <v>2798</v>
       </c>
@@ -6308,7 +6308,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A256">
         <v>2799</v>
       </c>
@@ -6331,7 +6331,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A257">
         <v>2800</v>
       </c>
@@ -6354,7 +6354,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A258">
         <v>2801</v>
       </c>
@@ -6377,7 +6377,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A259">
         <v>2802</v>
       </c>
@@ -6400,7 +6400,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A260">
         <v>2803</v>
       </c>
@@ -6423,7 +6423,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A261">
         <v>2804</v>
       </c>
@@ -6446,7 +6446,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A262">
         <v>2805</v>
       </c>
@@ -6469,7 +6469,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A263">
         <v>2806</v>
       </c>
@@ -6492,7 +6492,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A264">
         <v>2807</v>
       </c>
@@ -6515,7 +6515,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A265">
         <v>2808</v>
       </c>
@@ -6538,7 +6538,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A266">
         <v>2809</v>
       </c>
@@ -6561,7 +6561,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A267">
         <v>2810</v>
       </c>
@@ -6584,7 +6584,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A268">
         <v>2811</v>
       </c>
@@ -6607,7 +6607,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A269">
         <v>2812</v>
       </c>
@@ -6630,7 +6630,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A270">
         <v>2813</v>
       </c>
@@ -6653,7 +6653,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A271">
         <v>2814</v>
       </c>
@@ -6676,7 +6676,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A272">
         <v>2815</v>
       </c>
@@ -6699,7 +6699,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A273">
         <v>2816</v>
       </c>
@@ -6722,7 +6722,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A274">
         <v>2817</v>
       </c>
@@ -6745,7 +6745,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A275">
         <v>2818</v>
       </c>
@@ -6768,7 +6768,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A276">
         <v>2819</v>
       </c>
@@ -6791,7 +6791,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A277">
         <v>2820</v>
       </c>
@@ -6814,7 +6814,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A278">
         <v>2821</v>
       </c>
@@ -6837,7 +6837,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A279">
         <v>2822</v>
       </c>
@@ -6860,7 +6860,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A280">
         <v>2823</v>
       </c>
@@ -6883,7 +6883,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A281">
         <v>2824</v>
       </c>
@@ -6906,7 +6906,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A282">
         <v>2825</v>
       </c>
@@ -6929,7 +6929,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A283">
         <v>2826</v>
       </c>
@@ -6952,7 +6952,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A284">
         <v>2827</v>
       </c>
@@ -6975,7 +6975,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A285">
         <v>2828</v>
       </c>
@@ -6998,7 +6998,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A286">
         <v>2829</v>
       </c>
@@ -7021,7 +7021,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A287">
         <v>2830</v>
       </c>
@@ -7044,7 +7044,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A288">
         <v>2831</v>
       </c>
@@ -7067,7 +7067,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A289">
         <v>2832</v>
       </c>
@@ -7090,7 +7090,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A290">
         <v>2833</v>
       </c>
@@ -7113,7 +7113,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A291">
         <v>2834</v>
       </c>
@@ -7136,7 +7136,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A292">
         <v>2835</v>
       </c>
@@ -7159,7 +7159,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A293">
         <v>2836</v>
       </c>
@@ -7182,7 +7182,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A294">
         <v>2837</v>
       </c>
@@ -7205,7 +7205,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A295">
         <v>2838</v>
       </c>
@@ -7228,7 +7228,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A296">
         <v>2839</v>
       </c>
@@ -7251,7 +7251,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A297">
         <v>2840</v>
       </c>
@@ -7274,7 +7274,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A298">
         <v>2841</v>
       </c>
@@ -7297,7 +7297,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A299">
         <v>2842</v>
       </c>
@@ -7320,7 +7320,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A300">
         <v>2843</v>
       </c>
@@ -7343,7 +7343,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A301">
         <v>2844</v>
       </c>
@@ -7366,7 +7366,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A302">
         <v>2845</v>
       </c>
@@ -7389,7 +7389,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A303">
         <v>2846</v>
       </c>
@@ -7412,7 +7412,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A304">
         <v>2847</v>
       </c>
@@ -7435,7 +7435,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="305" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A305">
         <v>2848</v>
       </c>
@@ -7458,7 +7458,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="306" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A306">
         <v>2849</v>
       </c>
@@ -7481,7 +7481,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="307" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A307">
         <v>2850</v>
       </c>
@@ -7504,7 +7504,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="308" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A308">
         <v>2851</v>
       </c>
@@ -7527,7 +7527,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="309" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A309">
         <v>2852</v>
       </c>
@@ -7550,7 +7550,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="310" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A310">
         <v>2853</v>
       </c>
@@ -7573,7 +7573,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="311" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A311">
         <v>2854</v>
       </c>
@@ -7596,7 +7596,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="312" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A312">
         <v>2855</v>
       </c>
@@ -7619,7 +7619,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="313" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A313">
         <v>2856</v>
       </c>
@@ -7642,7 +7642,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="314" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A314">
         <v>2857</v>
       </c>
@@ -7665,7 +7665,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="315" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A315">
         <v>2858</v>
       </c>
@@ -7688,7 +7688,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="316" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A316">
         <v>2859</v>
       </c>
@@ -7711,7 +7711,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="317" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A317">
         <v>2860</v>
       </c>
@@ -7734,7 +7734,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="318" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A318">
         <v>2861</v>
       </c>
@@ -7757,7 +7757,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="319" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A319">
         <v>2862</v>
       </c>
@@ -7780,7 +7780,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="320" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A320">
         <v>2863</v>
       </c>
@@ -7803,7 +7803,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="321" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A321">
         <v>2864</v>
       </c>
@@ -7826,7 +7826,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="322" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A322">
         <v>2865</v>
       </c>
@@ -7849,7 +7849,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="323" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A323">
         <v>2866</v>
       </c>
@@ -7872,7 +7872,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="324" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A324">
         <v>2867</v>
       </c>
@@ -7895,7 +7895,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="325" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A325">
         <v>2868</v>
       </c>
@@ -7918,7 +7918,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="326" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A326">
         <v>2869</v>
       </c>
@@ -7941,7 +7941,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="327" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A327">
         <v>2870</v>
       </c>
@@ -7964,7 +7964,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="328" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A328">
         <v>2871</v>
       </c>
@@ -7987,7 +7987,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="329" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A329">
         <v>2872</v>
       </c>
@@ -8010,7 +8010,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="330" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A330">
         <v>2873</v>
       </c>
@@ -8033,7 +8033,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="331" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A331">
         <v>2874</v>
       </c>
@@ -8056,7 +8056,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="332" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A332">
         <v>2875</v>
       </c>
@@ -8079,7 +8079,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="333" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A333">
         <v>2876</v>
       </c>
@@ -8102,7 +8102,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="334" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A334">
         <v>2877</v>
       </c>
@@ -8125,7 +8125,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="335" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A335">
         <v>2878</v>
       </c>
@@ -8148,7 +8148,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="336" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A336">
         <v>2879</v>
       </c>
@@ -8171,7 +8171,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="337" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A337">
         <v>2880</v>
       </c>
@@ -8194,7 +8194,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="338" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A338">
         <v>2881</v>
       </c>
@@ -8217,7 +8217,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="339" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A339">
         <v>2882</v>
       </c>
@@ -8240,7 +8240,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="340" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A340">
         <v>2883</v>
       </c>
@@ -8263,7 +8263,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="341" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A341">
         <v>2884</v>
       </c>
@@ -8286,7 +8286,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="342" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A342">
         <v>2885</v>
       </c>
@@ -8309,7 +8309,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="343" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A343">
         <v>2886</v>
       </c>
@@ -8332,7 +8332,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="344" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A344">
         <v>2887</v>
       </c>
@@ -8355,7 +8355,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="345" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A345">
         <v>2888</v>
       </c>
@@ -8378,7 +8378,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="346" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A346">
         <v>2889</v>
       </c>
@@ -8401,7 +8401,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="347" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A347">
         <v>2890</v>
       </c>
@@ -8424,7 +8424,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="348" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A348">
         <v>2891</v>
       </c>
@@ -8447,7 +8447,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="349" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A349">
         <v>2892</v>
       </c>
@@ -8470,7 +8470,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="350" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A350">
         <v>2893</v>
       </c>
@@ -8493,7 +8493,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="351" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A351">
         <v>2894</v>
       </c>
@@ -8516,7 +8516,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="352" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A352">
         <v>2895</v>
       </c>
@@ -8539,7 +8539,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="353" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A353">
         <v>2896</v>
       </c>
@@ -8562,7 +8562,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="354" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A354">
         <v>2897</v>
       </c>
@@ -8585,7 +8585,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="355" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A355">
         <v>2898</v>
       </c>
@@ -8608,7 +8608,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="356" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A356">
         <v>2899</v>
       </c>
@@ -8631,7 +8631,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="357" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A357">
         <v>2900</v>
       </c>
@@ -8654,7 +8654,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="358" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A358">
         <v>2901</v>
       </c>
@@ -8677,7 +8677,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="359" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A359">
         <v>2902</v>
       </c>
@@ -8700,7 +8700,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="360" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A360">
         <v>2903</v>
       </c>
@@ -8723,7 +8723,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="361" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A361">
         <v>2904</v>
       </c>
@@ -8746,7 +8746,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="362" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A362">
         <v>2905</v>
       </c>
@@ -8769,7 +8769,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="363" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="363" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A363">
         <v>2906</v>
       </c>
@@ -8792,7 +8792,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="364" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A364">
         <v>2907</v>
       </c>
@@ -8815,7 +8815,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="365" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A365">
         <v>2908</v>
       </c>
@@ -8838,7 +8838,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="366" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="366" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A366">
         <v>2909</v>
       </c>
@@ -8861,7 +8861,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="367" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A367">
         <v>2910</v>
       </c>
@@ -8884,7 +8884,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="368" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A368">
         <v>2911</v>
       </c>
@@ -8907,7 +8907,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="369" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A369">
         <v>2912</v>
       </c>
@@ -8930,7 +8930,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="370" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A370">
         <v>2913</v>
       </c>
@@ -8953,7 +8953,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="371" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A371">
         <v>2914</v>
       </c>
@@ -8976,7 +8976,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="372" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A372">
         <v>2915</v>
       </c>
@@ -8999,7 +8999,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="373" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A373">
         <v>2916</v>
       </c>
@@ -9022,7 +9022,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="374" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A374">
         <v>2917</v>
       </c>
@@ -9045,7 +9045,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="375" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A375">
         <v>2918</v>
       </c>
@@ -9068,7 +9068,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="376" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A376">
         <v>2919</v>
       </c>
@@ -9091,7 +9091,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="377" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A377">
         <v>2920</v>
       </c>
@@ -9114,7 +9114,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="378" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A378">
         <v>2921</v>
       </c>
@@ -9137,7 +9137,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="379" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A379">
         <v>2922</v>
       </c>
@@ -9160,7 +9160,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="380" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A380">
         <v>2923</v>
       </c>
@@ -9183,7 +9183,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="381" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A381">
         <v>2924</v>
       </c>
@@ -9206,7 +9206,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="382" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A382">
         <v>2925</v>
       </c>
@@ -9229,7 +9229,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="383" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A383">
         <v>2926</v>
       </c>
@@ -9252,7 +9252,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="384" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="384" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A384">
         <v>2927</v>
       </c>
@@ -9275,7 +9275,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="385" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A385">
         <v>2928</v>
       </c>
@@ -9298,7 +9298,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="386" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A386">
         <v>2929</v>
       </c>
@@ -9321,7 +9321,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="387" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A387">
         <v>2930</v>
       </c>
@@ -9344,7 +9344,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="388" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="388" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A388">
         <v>2931</v>
       </c>
@@ -9367,7 +9367,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="389" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A389">
         <v>2932</v>
       </c>
@@ -9390,7 +9390,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="390" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A390">
         <v>2933</v>
       </c>
@@ -9413,7 +9413,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="391" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A391">
         <v>2934</v>
       </c>
@@ -9436,7 +9436,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="392" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A392">
         <v>2935</v>
       </c>
@@ -9459,7 +9459,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="393" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A393">
         <v>2936</v>
       </c>
@@ -9482,7 +9482,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="394" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A394">
         <v>2937</v>
       </c>
@@ -9505,7 +9505,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="395" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A395">
         <v>2938</v>
       </c>
@@ -9528,7 +9528,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="396" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A396">
         <v>2939</v>
       </c>
@@ -9551,7 +9551,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="397" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A397">
         <v>2940</v>
       </c>
@@ -9574,7 +9574,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="398" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A398">
         <v>2941</v>
       </c>
@@ -9597,7 +9597,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="399" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A399">
         <v>2942</v>
       </c>
@@ -9620,7 +9620,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="400" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="400" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A400">
         <v>2943</v>
       </c>
@@ -9643,7 +9643,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="401" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A401">
         <v>2944</v>
       </c>
@@ -9666,7 +9666,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="402" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="402" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A402">
         <v>2945</v>
       </c>
@@ -9689,7 +9689,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="403" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="403" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A403">
         <v>2946</v>
       </c>
@@ -9712,7 +9712,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="404" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="404" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A404">
         <v>2947</v>
       </c>
@@ -9735,7 +9735,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="405" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="405" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A405">
         <v>2948</v>
       </c>
@@ -9758,7 +9758,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="406" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="406" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A406">
         <v>2949</v>
       </c>
@@ -9781,7 +9781,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="407" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="407" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A407">
         <v>2950</v>
       </c>
@@ -9804,7 +9804,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="408" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="408" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A408">
         <v>2951</v>
       </c>
@@ -9827,7 +9827,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="409" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A409">
         <v>2952</v>
       </c>
@@ -9850,7 +9850,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="410" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A410">
         <v>2953</v>
       </c>
@@ -9873,7 +9873,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="411" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="411" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A411">
         <v>2954</v>
       </c>
@@ -9896,7 +9896,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="412" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="412" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A412">
         <v>2955</v>
       </c>
@@ -9919,7 +9919,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="413" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="413" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A413">
         <v>2956</v>
       </c>
@@ -9942,7 +9942,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="414" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="414" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A414">
         <v>2957</v>
       </c>
@@ -9965,7 +9965,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="415" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="415" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A415">
         <v>2958</v>
       </c>
@@ -9988,7 +9988,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="416" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="416" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A416">
         <v>2959</v>
       </c>
@@ -10011,7 +10011,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="417" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A417">
         <v>2960</v>
       </c>
@@ -10034,7 +10034,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="418" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A418">
         <v>2961</v>
       </c>
@@ -10057,7 +10057,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="419" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="419" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A419">
         <v>2962</v>
       </c>
@@ -10080,7 +10080,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="420" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A420">
         <v>2963</v>
       </c>
@@ -10103,7 +10103,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="421" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="421" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A421">
         <v>2964</v>
       </c>
@@ -10126,7 +10126,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="422" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="422" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A422">
         <v>2965</v>
       </c>
@@ -10149,7 +10149,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="423" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A423">
         <v>2966</v>
       </c>
@@ -10172,7 +10172,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="424" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="424" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A424">
         <v>2967</v>
       </c>
@@ -10195,7 +10195,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="425" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A425">
         <v>2968</v>
       </c>
@@ -10218,7 +10218,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="426" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="426" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A426">
         <v>2969</v>
       </c>
@@ -10241,7 +10241,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="427" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="427" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A427">
         <v>2970</v>
       </c>
@@ -10264,7 +10264,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="428" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="428" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A428">
         <v>2971</v>
       </c>
@@ -10287,7 +10287,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="429" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A429">
         <v>2972</v>
       </c>
@@ -10310,7 +10310,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="430" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="430" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A430">
         <v>2973</v>
       </c>
@@ -10333,7 +10333,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="431" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A431">
         <v>2974</v>
       </c>
@@ -10356,7 +10356,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="432" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A432">
         <v>2975</v>
       </c>
@@ -10377,6 +10377,397 @@
       </c>
       <c r="G432">
         <v>46</v>
+      </c>
+    </row>
+    <row r="433" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A433">
+        <v>2976</v>
+      </c>
+      <c r="B433">
+        <v>7</v>
+      </c>
+      <c r="C433">
+        <v>9</v>
+      </c>
+      <c r="D433">
+        <v>10</v>
+      </c>
+      <c r="E433">
+        <v>21</v>
+      </c>
+      <c r="F433">
+        <v>28</v>
+      </c>
+      <c r="G433">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="434" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A434">
+        <v>2977</v>
+      </c>
+      <c r="B434">
+        <v>8</v>
+      </c>
+      <c r="C434">
+        <v>19</v>
+      </c>
+      <c r="D434">
+        <v>27</v>
+      </c>
+      <c r="E434">
+        <v>32</v>
+      </c>
+      <c r="F434">
+        <v>38</v>
+      </c>
+      <c r="G434">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="435" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A435">
+        <v>2978</v>
+      </c>
+      <c r="B435">
+        <v>6</v>
+      </c>
+      <c r="C435">
+        <v>9</v>
+      </c>
+      <c r="D435">
+        <v>13</v>
+      </c>
+      <c r="E435">
+        <v>20</v>
+      </c>
+      <c r="F435">
+        <v>42</v>
+      </c>
+      <c r="G435">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="436" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A436">
+        <v>2979</v>
+      </c>
+      <c r="B436">
+        <v>18</v>
+      </c>
+      <c r="C436">
+        <v>27</v>
+      </c>
+      <c r="D436">
+        <v>37</v>
+      </c>
+      <c r="E436">
+        <v>43</v>
+      </c>
+      <c r="F436">
+        <v>47</v>
+      </c>
+      <c r="G436">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="437" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A437">
+        <v>2980</v>
+      </c>
+      <c r="B437">
+        <v>3</v>
+      </c>
+      <c r="C437">
+        <v>14</v>
+      </c>
+      <c r="D437">
+        <v>27</v>
+      </c>
+      <c r="E437">
+        <v>33</v>
+      </c>
+      <c r="F437">
+        <v>43</v>
+      </c>
+      <c r="G437">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="438" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A438">
+        <v>2981</v>
+      </c>
+      <c r="B438">
+        <v>15</v>
+      </c>
+      <c r="C438">
+        <v>22</v>
+      </c>
+      <c r="D438">
+        <v>27</v>
+      </c>
+      <c r="E438">
+        <v>32</v>
+      </c>
+      <c r="F438">
+        <v>50</v>
+      </c>
+      <c r="G438">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="439" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A439">
+        <v>2982</v>
+      </c>
+      <c r="B439">
+        <v>2</v>
+      </c>
+      <c r="C439">
+        <v>35</v>
+      </c>
+      <c r="D439">
+        <v>41</v>
+      </c>
+      <c r="E439">
+        <v>46</v>
+      </c>
+      <c r="F439">
+        <v>49</v>
+      </c>
+      <c r="G439">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="440" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A440">
+        <v>2983</v>
+      </c>
+      <c r="B440">
+        <v>3</v>
+      </c>
+      <c r="C440">
+        <v>15</v>
+      </c>
+      <c r="D440">
+        <v>30</v>
+      </c>
+      <c r="E440">
+        <v>32</v>
+      </c>
+      <c r="F440">
+        <v>40</v>
+      </c>
+      <c r="G440">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="441" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A441">
+        <v>2984</v>
+      </c>
+      <c r="B441">
+        <v>6</v>
+      </c>
+      <c r="C441">
+        <v>11</v>
+      </c>
+      <c r="D441">
+        <v>15</v>
+      </c>
+      <c r="E441">
+        <v>28</v>
+      </c>
+      <c r="F441">
+        <v>42</v>
+      </c>
+      <c r="G441">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="442" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A442">
+        <v>2985</v>
+      </c>
+      <c r="B442">
+        <v>6</v>
+      </c>
+      <c r="C442">
+        <v>8</v>
+      </c>
+      <c r="D442">
+        <v>21</v>
+      </c>
+      <c r="E442">
+        <v>32</v>
+      </c>
+      <c r="F442">
+        <v>41</v>
+      </c>
+      <c r="G442">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="443" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A443">
+        <v>2986</v>
+      </c>
+      <c r="B443">
+        <v>1</v>
+      </c>
+      <c r="C443">
+        <v>5</v>
+      </c>
+      <c r="D443">
+        <v>13</v>
+      </c>
+      <c r="E443">
+        <v>26</v>
+      </c>
+      <c r="F443">
+        <v>41</v>
+      </c>
+      <c r="G443">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="444" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A444">
+        <v>2987</v>
+      </c>
+      <c r="B444">
+        <v>16</v>
+      </c>
+      <c r="C444">
+        <v>17</v>
+      </c>
+      <c r="D444">
+        <v>20</v>
+      </c>
+      <c r="E444">
+        <v>28</v>
+      </c>
+      <c r="F444">
+        <v>46</v>
+      </c>
+      <c r="G444">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="445" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A445">
+        <v>2988</v>
+      </c>
+      <c r="B445">
+        <v>21</v>
+      </c>
+      <c r="C445">
+        <v>23</v>
+      </c>
+      <c r="D445">
+        <v>28</v>
+      </c>
+      <c r="E445">
+        <v>36</v>
+      </c>
+      <c r="F445">
+        <v>57</v>
+      </c>
+      <c r="G445">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="446" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A446">
+        <v>2989</v>
+      </c>
+      <c r="B446">
+        <v>6</v>
+      </c>
+      <c r="C446">
+        <v>14</v>
+      </c>
+      <c r="D446">
+        <v>28</v>
+      </c>
+      <c r="E446">
+        <v>31</v>
+      </c>
+      <c r="F446">
+        <v>56</v>
+      </c>
+      <c r="G446">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="447" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A447">
+        <v>2990</v>
+      </c>
+      <c r="B447">
+        <v>6</v>
+      </c>
+      <c r="C447">
+        <v>14</v>
+      </c>
+      <c r="D447">
+        <v>18</v>
+      </c>
+      <c r="E447">
+        <v>29</v>
+      </c>
+      <c r="F447">
+        <v>30</v>
+      </c>
+      <c r="G447">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="448" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A448">
+        <v>2991</v>
+      </c>
+      <c r="B448">
+        <v>4</v>
+      </c>
+      <c r="C448">
+        <v>14</v>
+      </c>
+      <c r="D448">
+        <v>19</v>
+      </c>
+      <c r="E448">
+        <v>23</v>
+      </c>
+      <c r="F448">
+        <v>36</v>
+      </c>
+      <c r="G448">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="449" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A449">
+        <v>2992</v>
+      </c>
+      <c r="B449">
+        <v>4</v>
+      </c>
+      <c r="C449">
+        <v>17</v>
+      </c>
+      <c r="D449">
+        <v>23</v>
+      </c>
+      <c r="E449">
+        <v>33</v>
+      </c>
+      <c r="F449">
+        <v>36</v>
+      </c>
+      <c r="G449">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -10386,6 +10777,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -10553,15 +10953,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -10573,6 +10964,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9445F805-6E3A-4841-AEBD-CF7F6CDA924D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10592,14 +10991,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64615F65-CF13-4100-B135-FA0CB5E1C951}">
   <ds:schemaRefs>

--- a/LoteriasExcel/MegaSena_edt.xlsx
+++ b/LoteriasExcel/MegaSena_edt.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66B927D0-3D03-46BC-9874-89B2CDA9EED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{326EA327-4C27-4B76-A42B-F488EB40AC08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="58335" yWindow="735" windowWidth="10545" windowHeight="10425" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="MEGA SENA" sheetId="4" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -434,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA4E33BD-754C-4CC3-9530-49E6C4C5E994}">
-  <dimension ref="A1:G449"/>
+  <dimension ref="A1:G456"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.06640625" customWidth="1"/>
@@ -10770,6 +10770,167 @@
         <v>49</v>
       </c>
     </row>
+    <row r="450" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A450">
+        <v>2993</v>
+      </c>
+      <c r="B450">
+        <v>3</v>
+      </c>
+      <c r="C450">
+        <v>15</v>
+      </c>
+      <c r="D450">
+        <v>31</v>
+      </c>
+      <c r="E450">
+        <v>42</v>
+      </c>
+      <c r="F450">
+        <v>43</v>
+      </c>
+      <c r="G450">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="451" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A451">
+        <v>2994</v>
+      </c>
+      <c r="B451">
+        <v>1</v>
+      </c>
+      <c r="C451">
+        <v>10</v>
+      </c>
+      <c r="D451">
+        <v>23</v>
+      </c>
+      <c r="E451">
+        <v>31</v>
+      </c>
+      <c r="F451">
+        <v>40</v>
+      </c>
+      <c r="G451">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="452" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A452">
+        <v>2995</v>
+      </c>
+      <c r="B452">
+        <v>8</v>
+      </c>
+      <c r="C452">
+        <v>29</v>
+      </c>
+      <c r="D452">
+        <v>42</v>
+      </c>
+      <c r="E452">
+        <v>49</v>
+      </c>
+      <c r="F452">
+        <v>50</v>
+      </c>
+      <c r="G452">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="453" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A453">
+        <v>2996</v>
+      </c>
+      <c r="B453">
+        <v>7</v>
+      </c>
+      <c r="C453">
+        <v>9</v>
+      </c>
+      <c r="D453">
+        <v>27</v>
+      </c>
+      <c r="E453">
+        <v>38</v>
+      </c>
+      <c r="F453">
+        <v>49</v>
+      </c>
+      <c r="G453">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="454" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A454">
+        <v>2997</v>
+      </c>
+      <c r="B454">
+        <v>14</v>
+      </c>
+      <c r="C454">
+        <v>20</v>
+      </c>
+      <c r="D454">
+        <v>32</v>
+      </c>
+      <c r="E454">
+        <v>37</v>
+      </c>
+      <c r="F454">
+        <v>39</v>
+      </c>
+      <c r="G454">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="455" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A455">
+        <v>2998</v>
+      </c>
+      <c r="B455">
+        <v>15</v>
+      </c>
+      <c r="C455">
+        <v>18</v>
+      </c>
+      <c r="D455">
+        <v>28</v>
+      </c>
+      <c r="E455">
+        <v>31</v>
+      </c>
+      <c r="F455">
+        <v>52</v>
+      </c>
+      <c r="G455">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="456" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A456">
+        <v>2999</v>
+      </c>
+      <c r="B456">
+        <v>9</v>
+      </c>
+      <c r="C456">
+        <v>24</v>
+      </c>
+      <c r="D456">
+        <v>26</v>
+      </c>
+      <c r="E456">
+        <v>38</v>
+      </c>
+      <c r="F456">
+        <v>45</v>
+      </c>
+      <c r="G456">
+        <v>58</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -10777,15 +10938,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -10953,6 +11105,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -10964,14 +11125,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9445F805-6E3A-4841-AEBD-CF7F6CDA924D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10991,6 +11144,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64615F65-CF13-4100-B135-FA0CB5E1C951}">
   <ds:schemaRefs>

--- a/LoteriasExcel/MegaSena_edt.xlsx
+++ b/LoteriasExcel/MegaSena_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{326EA327-4C27-4B76-A42B-F488EB40AC08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EFB3FB1-F09F-4715-B629-433B4BF54D12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="58335" yWindow="735" windowWidth="10545" windowHeight="10425" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="66855" yWindow="810" windowWidth="18675" windowHeight="12840" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="MEGA SENA" sheetId="4" r:id="rId1"/>
@@ -434,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA4E33BD-754C-4CC3-9530-49E6C4C5E994}">
-  <dimension ref="A1:G456"/>
+  <dimension ref="A1:G457"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.06640625" customWidth="1"/>
@@ -10931,6 +10931,29 @@
         <v>58</v>
       </c>
     </row>
+    <row r="457" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A457">
+        <v>3000</v>
+      </c>
+      <c r="B457">
+        <v>22</v>
+      </c>
+      <c r="C457">
+        <v>23</v>
+      </c>
+      <c r="D457">
+        <v>36</v>
+      </c>
+      <c r="E457">
+        <v>40</v>
+      </c>
+      <c r="F457">
+        <v>52</v>
+      </c>
+      <c r="G457">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -10938,6 +10961,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -11105,15 +11137,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -11125,6 +11148,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9445F805-6E3A-4841-AEBD-CF7F6CDA924D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11144,14 +11175,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64615F65-CF13-4100-B135-FA0CB5E1C951}">
   <ds:schemaRefs>

--- a/LoteriasExcel/MegaSena_edt.xlsx
+++ b/LoteriasExcel/MegaSena_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EFB3FB1-F09F-4715-B629-433B4BF54D12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE94EE40-5543-4651-812E-D97DC554B909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="66855" yWindow="810" windowWidth="18675" windowHeight="12840" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="57555" yWindow="330" windowWidth="19590" windowHeight="12510" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="MEGA SENA" sheetId="4" r:id="rId1"/>
@@ -434,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA4E33BD-754C-4CC3-9530-49E6C4C5E994}">
-  <dimension ref="A1:G457"/>
+  <dimension ref="A1:G462"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.06640625" customWidth="1"/>
@@ -10954,6 +10954,118 @@
         <v>60</v>
       </c>
     </row>
+    <row r="458" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A458">
+        <v>3002</v>
+      </c>
+      <c r="B458">
+        <v>1</v>
+      </c>
+      <c r="C458">
+        <v>13</v>
+      </c>
+      <c r="D458">
+        <v>32</v>
+      </c>
+      <c r="E458">
+        <v>36</v>
+      </c>
+      <c r="F458">
+        <v>43</v>
+      </c>
+      <c r="G458">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="459" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A459">
+        <v>3003</v>
+      </c>
+      <c r="B459">
+        <v>4</v>
+      </c>
+      <c r="C459">
+        <v>27</v>
+      </c>
+      <c r="D459">
+        <v>51</v>
+      </c>
+      <c r="E459">
+        <v>52</v>
+      </c>
+      <c r="F459">
+        <v>54</v>
+      </c>
+      <c r="G459">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="460" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A460">
+        <v>3004</v>
+      </c>
+      <c r="B460">
+        <v>8</v>
+      </c>
+      <c r="C460">
+        <v>24</v>
+      </c>
+      <c r="D460">
+        <v>27</v>
+      </c>
+      <c r="E460">
+        <v>37</v>
+      </c>
+      <c r="F460">
+        <v>47</v>
+      </c>
+      <c r="G460">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="461" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A461">
+        <v>3005</v>
+      </c>
+      <c r="B461">
+        <v>1</v>
+      </c>
+      <c r="C461">
+        <v>5</v>
+      </c>
+      <c r="D461">
+        <v>7</v>
+      </c>
+      <c r="E461">
+        <v>22</v>
+      </c>
+      <c r="F461">
+        <v>50</v>
+      </c>
+      <c r="G461">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="462" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="B462">
+        <v>17</v>
+      </c>
+      <c r="C462">
+        <v>23</v>
+      </c>
+      <c r="D462">
+        <v>29</v>
+      </c>
+      <c r="E462">
+        <v>30</v>
+      </c>
+      <c r="F462">
+        <v>48</v>
+      </c>
+      <c r="G462">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -10961,15 +11073,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -11137,6 +11240,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -11148,14 +11260,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9445F805-6E3A-4841-AEBD-CF7F6CDA924D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11175,6 +11279,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64615F65-CF13-4100-B135-FA0CB5E1C951}">
   <ds:schemaRefs>

--- a/LoteriasExcel/MegaSena_edt.xlsx
+++ b/LoteriasExcel/MegaSena_edt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE94EE40-5543-4651-812E-D97DC554B909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{325CF401-43BB-4F96-956D-1CB39293DCE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57555" yWindow="330" windowWidth="19590" windowHeight="12510" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="57705" yWindow="1680" windowWidth="15285" windowHeight="13395" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="MEGA SENA" sheetId="4" r:id="rId1"/>
@@ -434,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA4E33BD-754C-4CC3-9530-49E6C4C5E994}">
-  <dimension ref="A1:G462"/>
+  <dimension ref="A1:G478"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.06640625" customWidth="1"/>
@@ -10956,7 +10956,7 @@
     </row>
     <row r="458" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A458">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="B458">
         <v>1</v>
@@ -10979,7 +10979,7 @@
     </row>
     <row r="459" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A459">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="B459">
         <v>4</v>
@@ -11002,7 +11002,7 @@
     </row>
     <row r="460" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A460">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="B460">
         <v>8</v>
@@ -11025,7 +11025,7 @@
     </row>
     <row r="461" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A461">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="B461">
         <v>1</v>
@@ -11047,6 +11047,9 @@
       </c>
     </row>
     <row r="462" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A462">
+        <v>3005</v>
+      </c>
       <c r="B462">
         <v>17</v>
       </c>
@@ -11064,6 +11067,374 @@
       </c>
       <c r="G462">
         <v>50</v>
+      </c>
+    </row>
+    <row r="463" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A463">
+        <v>3006</v>
+      </c>
+      <c r="B463">
+        <v>25</v>
+      </c>
+      <c r="C463">
+        <v>42</v>
+      </c>
+      <c r="D463">
+        <v>45</v>
+      </c>
+      <c r="E463">
+        <v>48</v>
+      </c>
+      <c r="F463">
+        <v>50</v>
+      </c>
+      <c r="G463">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="464" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A464">
+        <v>3007</v>
+      </c>
+      <c r="B464">
+        <v>17</v>
+      </c>
+      <c r="C464">
+        <v>19</v>
+      </c>
+      <c r="D464">
+        <v>27</v>
+      </c>
+      <c r="E464">
+        <v>32</v>
+      </c>
+      <c r="F464">
+        <v>38</v>
+      </c>
+      <c r="G464">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="465" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A465">
+        <v>3008</v>
+      </c>
+      <c r="B465">
+        <v>11</v>
+      </c>
+      <c r="C465">
+        <v>12</v>
+      </c>
+      <c r="D465">
+        <v>14</v>
+      </c>
+      <c r="E465">
+        <v>20</v>
+      </c>
+      <c r="F465">
+        <v>42</v>
+      </c>
+      <c r="G465">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="466" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A466">
+        <v>3009</v>
+      </c>
+      <c r="B466">
+        <v>4</v>
+      </c>
+      <c r="C466">
+        <v>6</v>
+      </c>
+      <c r="D466">
+        <v>8</v>
+      </c>
+      <c r="E466">
+        <v>18</v>
+      </c>
+      <c r="F466">
+        <v>21</v>
+      </c>
+      <c r="G466">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="467" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A467">
+        <v>3010</v>
+      </c>
+      <c r="B467">
+        <v>3</v>
+      </c>
+      <c r="C467">
+        <v>30</v>
+      </c>
+      <c r="D467">
+        <v>33</v>
+      </c>
+      <c r="E467">
+        <v>35</v>
+      </c>
+      <c r="F467">
+        <v>45</v>
+      </c>
+      <c r="G467">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="468" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A468">
+        <v>3011</v>
+      </c>
+      <c r="B468">
+        <v>2</v>
+      </c>
+      <c r="C468">
+        <v>5</v>
+      </c>
+      <c r="D468">
+        <v>27</v>
+      </c>
+      <c r="E468">
+        <v>36</v>
+      </c>
+      <c r="F468">
+        <v>40</v>
+      </c>
+      <c r="G468">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="469" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A469">
+        <v>3012</v>
+      </c>
+      <c r="B469">
+        <v>5</v>
+      </c>
+      <c r="C469">
+        <v>7</v>
+      </c>
+      <c r="D469">
+        <v>17</v>
+      </c>
+      <c r="E469">
+        <v>41</v>
+      </c>
+      <c r="F469">
+        <v>42</v>
+      </c>
+      <c r="G469">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="470" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A470">
+        <v>3013</v>
+      </c>
+      <c r="B470">
+        <v>2</v>
+      </c>
+      <c r="C470">
+        <v>14</v>
+      </c>
+      <c r="D470">
+        <v>21</v>
+      </c>
+      <c r="E470">
+        <v>22</v>
+      </c>
+      <c r="F470">
+        <v>34</v>
+      </c>
+      <c r="G470">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="471" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A471">
+        <v>3014</v>
+      </c>
+      <c r="B471">
+        <v>27</v>
+      </c>
+      <c r="C471">
+        <v>30</v>
+      </c>
+      <c r="D471">
+        <v>35</v>
+      </c>
+      <c r="E471">
+        <v>40</v>
+      </c>
+      <c r="F471">
+        <v>44</v>
+      </c>
+      <c r="G471">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="472" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A472">
+        <v>3015</v>
+      </c>
+      <c r="B472">
+        <v>9</v>
+      </c>
+      <c r="C472">
+        <v>18</v>
+      </c>
+      <c r="D472">
+        <v>26</v>
+      </c>
+      <c r="E472">
+        <v>31</v>
+      </c>
+      <c r="F472">
+        <v>53</v>
+      </c>
+      <c r="G472">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="473" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A473">
+        <v>3016</v>
+      </c>
+      <c r="B473">
+        <v>11</v>
+      </c>
+      <c r="C473">
+        <v>19</v>
+      </c>
+      <c r="D473">
+        <v>33</v>
+      </c>
+      <c r="E473">
+        <v>52</v>
+      </c>
+      <c r="F473">
+        <v>55</v>
+      </c>
+      <c r="G473">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="474" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A474">
+        <v>3017</v>
+      </c>
+      <c r="B474">
+        <v>4</v>
+      </c>
+      <c r="C474">
+        <v>6</v>
+      </c>
+      <c r="D474">
+        <v>26</v>
+      </c>
+      <c r="E474">
+        <v>28</v>
+      </c>
+      <c r="F474">
+        <v>32</v>
+      </c>
+      <c r="G474">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="475" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A475">
+        <v>3018</v>
+      </c>
+      <c r="B475">
+        <v>5</v>
+      </c>
+      <c r="C475">
+        <v>6</v>
+      </c>
+      <c r="D475">
+        <v>17</v>
+      </c>
+      <c r="E475">
+        <v>27</v>
+      </c>
+      <c r="F475">
+        <v>57</v>
+      </c>
+      <c r="G475">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="476" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A476">
+        <v>3019</v>
+      </c>
+      <c r="B476">
+        <v>5</v>
+      </c>
+      <c r="C476">
+        <v>31</v>
+      </c>
+      <c r="D476">
+        <v>32</v>
+      </c>
+      <c r="E476">
+        <v>48</v>
+      </c>
+      <c r="F476">
+        <v>54</v>
+      </c>
+      <c r="G476">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="477" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A477">
+        <v>3020</v>
+      </c>
+      <c r="B477">
+        <v>6</v>
+      </c>
+      <c r="C477">
+        <v>9</v>
+      </c>
+      <c r="D477">
+        <v>17</v>
+      </c>
+      <c r="E477">
+        <v>27</v>
+      </c>
+      <c r="F477">
+        <v>29</v>
+      </c>
+      <c r="G477">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="478" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A478">
+        <v>3021</v>
+      </c>
+      <c r="B478">
+        <v>16</v>
+      </c>
+      <c r="C478">
+        <v>19</v>
+      </c>
+      <c r="D478">
+        <v>22</v>
+      </c>
+      <c r="E478">
+        <v>24</v>
+      </c>
+      <c r="F478">
+        <v>46</v>
+      </c>
+      <c r="G478">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -11073,6 +11444,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -11240,15 +11620,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -11260,6 +11631,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9445F805-6E3A-4841-AEBD-CF7F6CDA924D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11279,14 +11658,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64615F65-CF13-4100-B135-FA0CB5E1C951}">
   <ds:schemaRefs>

--- a/LoteriasExcel/MegaSena_edt.xlsx
+++ b/LoteriasExcel/MegaSena_edt.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{325CF401-43BB-4F96-956D-1CB39293DCE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32C4F64E-AA88-4B6D-A765-A81F70AF5543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57705" yWindow="1680" windowWidth="15285" windowHeight="13395" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="59100" yWindow="390" windowWidth="12750" windowHeight="15165" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="MEGA SENA" sheetId="4" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -434,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA4E33BD-754C-4CC3-9530-49E6C4C5E994}">
-  <dimension ref="A1:G478"/>
+  <dimension ref="A1:G480"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.06640625" customWidth="1"/>
@@ -11437,6 +11437,52 @@
         <v>58</v>
       </c>
     </row>
+    <row r="479" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A479">
+        <v>3022</v>
+      </c>
+      <c r="B479">
+        <v>2</v>
+      </c>
+      <c r="C479">
+        <v>3</v>
+      </c>
+      <c r="D479">
+        <v>8</v>
+      </c>
+      <c r="E479">
+        <v>11</v>
+      </c>
+      <c r="F479">
+        <v>17</v>
+      </c>
+      <c r="G479">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="480" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A480">
+        <v>3023</v>
+      </c>
+      <c r="B480">
+        <v>22</v>
+      </c>
+      <c r="C480">
+        <v>25</v>
+      </c>
+      <c r="D480">
+        <v>30</v>
+      </c>
+      <c r="E480">
+        <v>31</v>
+      </c>
+      <c r="F480">
+        <v>39</v>
+      </c>
+      <c r="G480">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -11444,15 +11490,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -11620,6 +11657,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -11631,14 +11677,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9445F805-6E3A-4841-AEBD-CF7F6CDA924D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11658,6 +11696,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64615F65-CF13-4100-B135-FA0CB5E1C951}">
   <ds:schemaRefs>

--- a/LoteriasExcel/MegaSena_edt.xlsx
+++ b/LoteriasExcel/MegaSena_edt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32C4F64E-AA88-4B6D-A765-A81F70AF5543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15019BB0-1058-4F3A-8304-26E7393FEE8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="59100" yWindow="390" windowWidth="12750" windowHeight="15165" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="58230" yWindow="825" windowWidth="19515" windowHeight="14565" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="MEGA SENA" sheetId="4" r:id="rId1"/>
@@ -109,11 +109,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -434,7 +436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA4E33BD-754C-4CC3-9530-49E6C4C5E994}">
-  <dimension ref="A1:G480"/>
+  <dimension ref="A1:G481"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.06640625" customWidth="1"/>
@@ -11483,6 +11485,29 @@
         <v>60</v>
       </c>
     </row>
+    <row r="481" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A481" s="2">
+        <v>3024</v>
+      </c>
+      <c r="B481" s="3">
+        <v>13</v>
+      </c>
+      <c r="C481" s="3">
+        <v>39</v>
+      </c>
+      <c r="D481" s="3">
+        <v>42</v>
+      </c>
+      <c r="E481" s="3">
+        <v>44</v>
+      </c>
+      <c r="F481" s="3">
+        <v>47</v>
+      </c>
+      <c r="G481" s="3">
+        <v>49</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -11490,6 +11515,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -11657,15 +11691,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -11677,6 +11702,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9445F805-6E3A-4841-AEBD-CF7F6CDA924D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11696,14 +11729,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64615F65-CF13-4100-B135-FA0CB5E1C951}">
   <ds:schemaRefs>

--- a/LoteriasExcel/MegaSena_edt.xlsx
+++ b/LoteriasExcel/MegaSena_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15019BB0-1058-4F3A-8304-26E7393FEE8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2356B6AA-FC17-4A6A-AB7F-84D3913077EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="58230" yWindow="825" windowWidth="19515" windowHeight="14565" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="57480" yWindow="2910" windowWidth="19770" windowHeight="11130" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="MEGA SENA" sheetId="4" r:id="rId1"/>
@@ -436,7 +436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA4E33BD-754C-4CC3-9530-49E6C4C5E994}">
-  <dimension ref="A1:G481"/>
+  <dimension ref="A1:G485"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.06640625" customWidth="1"/>
@@ -11486,26 +11486,118 @@
       </c>
     </row>
     <row r="481" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A481" s="2">
+      <c r="A481">
         <v>3024</v>
       </c>
-      <c r="B481" s="3">
+      <c r="B481">
         <v>13</v>
       </c>
-      <c r="C481" s="3">
+      <c r="C481">
         <v>39</v>
       </c>
-      <c r="D481" s="3">
+      <c r="D481">
         <v>42</v>
       </c>
-      <c r="E481" s="3">
+      <c r="E481">
         <v>44</v>
       </c>
-      <c r="F481" s="3">
+      <c r="F481">
         <v>47</v>
       </c>
-      <c r="G481" s="3">
+      <c r="G481">
         <v>49</v>
+      </c>
+    </row>
+    <row r="482" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A482" s="2">
+        <v>3025</v>
+      </c>
+      <c r="B482" s="3">
+        <v>7</v>
+      </c>
+      <c r="C482" s="3">
+        <v>14</v>
+      </c>
+      <c r="D482" s="3">
+        <v>16</v>
+      </c>
+      <c r="E482" s="3">
+        <v>21</v>
+      </c>
+      <c r="F482" s="3">
+        <v>33</v>
+      </c>
+      <c r="G482" s="3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="483" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A483" s="2">
+        <v>3026</v>
+      </c>
+      <c r="B483" s="3">
+        <v>14</v>
+      </c>
+      <c r="C483" s="3">
+        <v>19</v>
+      </c>
+      <c r="D483" s="3">
+        <v>42</v>
+      </c>
+      <c r="E483" s="3">
+        <v>45</v>
+      </c>
+      <c r="F483" s="3">
+        <v>48</v>
+      </c>
+      <c r="G483" s="3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="484" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A484" s="2">
+        <v>3027</v>
+      </c>
+      <c r="B484" s="3">
+        <v>6</v>
+      </c>
+      <c r="C484" s="3">
+        <v>15</v>
+      </c>
+      <c r="D484" s="3">
+        <v>16</v>
+      </c>
+      <c r="E484" s="3">
+        <v>24</v>
+      </c>
+      <c r="F484" s="3">
+        <v>34</v>
+      </c>
+      <c r="G484" s="3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="485" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A485" s="2">
+        <v>3028</v>
+      </c>
+      <c r="B485" s="3">
+        <v>2</v>
+      </c>
+      <c r="C485" s="3">
+        <v>10</v>
+      </c>
+      <c r="D485" s="3">
+        <v>11</v>
+      </c>
+      <c r="E485" s="3">
+        <v>25</v>
+      </c>
+      <c r="F485" s="3">
+        <v>51</v>
+      </c>
+      <c r="G485" s="3">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -11515,15 +11607,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -11691,6 +11774,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -11702,14 +11794,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9445F805-6E3A-4841-AEBD-CF7F6CDA924D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11729,6 +11813,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64615F65-CF13-4100-B135-FA0CB5E1C951}">
   <ds:schemaRefs>

--- a/LoteriasExcel/MegaSena_edt.xlsx
+++ b/LoteriasExcel/MegaSena_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2356B6AA-FC17-4A6A-AB7F-84D3913077EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CAEA6C7-1E32-4FAC-BF63-F3A124A928E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="2910" windowWidth="19770" windowHeight="11130" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="61245" yWindow="870" windowWidth="19770" windowHeight="11130" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="MEGA SENA" sheetId="4" r:id="rId1"/>
@@ -109,13 +109,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -436,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA4E33BD-754C-4CC3-9530-49E6C4C5E994}">
-  <dimension ref="A1:G485"/>
+  <dimension ref="A1:G486"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.06640625" customWidth="1"/>
@@ -11509,95 +11507,118 @@
       </c>
     </row>
     <row r="482" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A482" s="2">
+      <c r="A482">
         <v>3025</v>
       </c>
-      <c r="B482" s="3">
+      <c r="B482">
         <v>7</v>
       </c>
-      <c r="C482" s="3">
+      <c r="C482">
         <v>14</v>
       </c>
-      <c r="D482" s="3">
+      <c r="D482">
         <v>16</v>
       </c>
-      <c r="E482" s="3">
+      <c r="E482">
         <v>21</v>
       </c>
-      <c r="F482" s="3">
+      <c r="F482">
         <v>33</v>
       </c>
-      <c r="G482" s="3">
+      <c r="G482">
         <v>58</v>
       </c>
     </row>
     <row r="483" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A483" s="2">
+      <c r="A483">
         <v>3026</v>
       </c>
-      <c r="B483" s="3">
+      <c r="B483">
         <v>14</v>
       </c>
-      <c r="C483" s="3">
+      <c r="C483">
         <v>19</v>
       </c>
-      <c r="D483" s="3">
+      <c r="D483">
         <v>42</v>
       </c>
-      <c r="E483" s="3">
+      <c r="E483">
         <v>45</v>
       </c>
-      <c r="F483" s="3">
+      <c r="F483">
         <v>48</v>
       </c>
-      <c r="G483" s="3">
+      <c r="G483">
         <v>54</v>
       </c>
     </row>
     <row r="484" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A484" s="2">
+      <c r="A484">
         <v>3027</v>
       </c>
-      <c r="B484" s="3">
+      <c r="B484">
         <v>6</v>
       </c>
-      <c r="C484" s="3">
+      <c r="C484">
         <v>15</v>
       </c>
-      <c r="D484" s="3">
+      <c r="D484">
         <v>16</v>
       </c>
-      <c r="E484" s="3">
+      <c r="E484">
         <v>24</v>
       </c>
-      <c r="F484" s="3">
+      <c r="F484">
         <v>34</v>
       </c>
-      <c r="G484" s="3">
+      <c r="G484">
         <v>47</v>
       </c>
     </row>
     <row r="485" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A485" s="2">
+      <c r="A485">
         <v>3028</v>
       </c>
-      <c r="B485" s="3">
+      <c r="B485">
         <v>2</v>
       </c>
-      <c r="C485" s="3">
+      <c r="C485">
         <v>10</v>
       </c>
-      <c r="D485" s="3">
+      <c r="D485">
         <v>11</v>
       </c>
-      <c r="E485" s="3">
+      <c r="E485">
         <v>25</v>
       </c>
-      <c r="F485" s="3">
+      <c r="F485">
         <v>51</v>
       </c>
-      <c r="G485" s="3">
+      <c r="G485">
         <v>56</v>
+      </c>
+    </row>
+    <row r="486" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A486">
+        <v>3029</v>
+      </c>
+      <c r="B486">
+        <v>1</v>
+      </c>
+      <c r="C486">
+        <v>11</v>
+      </c>
+      <c r="D486">
+        <v>24</v>
+      </c>
+      <c r="E486">
+        <v>33</v>
+      </c>
+      <c r="F486">
+        <v>35</v>
+      </c>
+      <c r="G486">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -11607,6 +11628,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -11774,15 +11804,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -11794,6 +11815,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9445F805-6E3A-4841-AEBD-CF7F6CDA924D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11813,14 +11842,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64615F65-CF13-4100-B135-FA0CB5E1C951}">
   <ds:schemaRefs>

--- a/LoteriasExcel/MegaSena_edt.xlsx
+++ b/LoteriasExcel/MegaSena_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CAEA6C7-1E32-4FAC-BF63-F3A124A928E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE13C7D7-67F5-475B-A4B7-498FD699BABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="61245" yWindow="870" windowWidth="19770" windowHeight="11130" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="59415" yWindow="135" windowWidth="26985" windowHeight="7695" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="MEGA SENA" sheetId="4" r:id="rId1"/>
@@ -109,11 +109,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -434,7 +436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA4E33BD-754C-4CC3-9530-49E6C4C5E994}">
-  <dimension ref="A1:G486"/>
+  <dimension ref="A1:G488"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.06640625" customWidth="1"/>
@@ -11621,6 +11623,52 @@
         <v>59</v>
       </c>
     </row>
+    <row r="487" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A487" s="2">
+        <v>3030</v>
+      </c>
+      <c r="B487" s="3">
+        <v>6</v>
+      </c>
+      <c r="C487" s="3">
+        <v>11</v>
+      </c>
+      <c r="D487" s="3">
+        <v>25</v>
+      </c>
+      <c r="E487" s="3">
+        <v>45</v>
+      </c>
+      <c r="F487" s="3">
+        <v>48</v>
+      </c>
+      <c r="G487" s="3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="488" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A488" s="2">
+        <v>3031</v>
+      </c>
+      <c r="B488" s="3">
+        <v>20</v>
+      </c>
+      <c r="C488" s="3">
+        <v>28</v>
+      </c>
+      <c r="D488" s="3">
+        <v>32</v>
+      </c>
+      <c r="E488" s="3">
+        <v>35</v>
+      </c>
+      <c r="F488" s="3">
+        <v>40</v>
+      </c>
+      <c r="G488" s="3">
+        <v>54</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -11628,15 +11676,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -11804,6 +11843,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -11815,14 +11863,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9445F805-6E3A-4841-AEBD-CF7F6CDA924D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11842,6 +11882,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64615F65-CF13-4100-B135-FA0CB5E1C951}">
   <ds:schemaRefs>

--- a/LoteriasExcel/MegaSena_edt.xlsx
+++ b/LoteriasExcel/MegaSena_edt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE13C7D7-67F5-475B-A4B7-498FD699BABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D54432-D0C7-4852-85D6-FF20C35EA65C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="59415" yWindow="135" windowWidth="26985" windowHeight="7695" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="997" yWindow="727" windowWidth="22036" windowHeight="10313" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="MEGA SENA" sheetId="4" r:id="rId1"/>
@@ -436,7 +436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA4E33BD-754C-4CC3-9530-49E6C4C5E994}">
-  <dimension ref="A1:G488"/>
+  <dimension ref="A1:G494"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.06640625" customWidth="1"/>
@@ -11624,48 +11624,186 @@
       </c>
     </row>
     <row r="487" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A487" s="2">
+      <c r="A487">
         <v>3030</v>
       </c>
-      <c r="B487" s="3">
+      <c r="B487">
         <v>6</v>
       </c>
-      <c r="C487" s="3">
+      <c r="C487">
         <v>11</v>
       </c>
-      <c r="D487" s="3">
+      <c r="D487">
         <v>25</v>
       </c>
-      <c r="E487" s="3">
+      <c r="E487">
         <v>45</v>
       </c>
-      <c r="F487" s="3">
+      <c r="F487">
         <v>48</v>
       </c>
-      <c r="G487" s="3">
+      <c r="G487">
         <v>58</v>
       </c>
     </row>
     <row r="488" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A488" s="2">
+      <c r="A488">
         <v>3031</v>
       </c>
-      <c r="B488" s="3">
+      <c r="B488">
         <v>20</v>
       </c>
-      <c r="C488" s="3">
+      <c r="C488">
         <v>28</v>
       </c>
-      <c r="D488" s="3">
+      <c r="D488">
         <v>32</v>
       </c>
-      <c r="E488" s="3">
+      <c r="E488">
         <v>35</v>
       </c>
-      <c r="F488" s="3">
+      <c r="F488">
         <v>40</v>
       </c>
-      <c r="G488" s="3">
+      <c r="G488">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="489" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A489" s="2">
+        <v>3032</v>
+      </c>
+      <c r="B489" s="3">
+        <v>8</v>
+      </c>
+      <c r="C489" s="3">
+        <v>12</v>
+      </c>
+      <c r="D489" s="3">
+        <v>23</v>
+      </c>
+      <c r="E489" s="3">
+        <v>27</v>
+      </c>
+      <c r="F489" s="3">
+        <v>42</v>
+      </c>
+      <c r="G489" s="3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="490" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A490" s="2">
+        <v>3033</v>
+      </c>
+      <c r="B490" s="3">
+        <v>18</v>
+      </c>
+      <c r="C490" s="3">
+        <v>21</v>
+      </c>
+      <c r="D490" s="3">
+        <v>23</v>
+      </c>
+      <c r="E490" s="3">
+        <v>43</v>
+      </c>
+      <c r="F490" s="3">
+        <v>55</v>
+      </c>
+      <c r="G490" s="3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="491" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A491" s="2">
+        <v>3034</v>
+      </c>
+      <c r="B491" s="3">
+        <v>8</v>
+      </c>
+      <c r="C491" s="3">
+        <v>28</v>
+      </c>
+      <c r="D491" s="3">
+        <v>30</v>
+      </c>
+      <c r="E491" s="3">
+        <v>37</v>
+      </c>
+      <c r="F491" s="3">
+        <v>39</v>
+      </c>
+      <c r="G491" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="492" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A492" s="2">
+        <v>3035</v>
+      </c>
+      <c r="B492" s="3">
+        <v>5</v>
+      </c>
+      <c r="C492" s="3">
+        <v>7</v>
+      </c>
+      <c r="D492" s="3">
+        <v>17</v>
+      </c>
+      <c r="E492" s="3">
+        <v>51</v>
+      </c>
+      <c r="F492" s="3">
+        <v>56</v>
+      </c>
+      <c r="G492" s="3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="493" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A493" s="2">
+        <v>3036</v>
+      </c>
+      <c r="B493" s="3">
+        <v>5</v>
+      </c>
+      <c r="C493" s="3">
+        <v>12</v>
+      </c>
+      <c r="D493" s="3">
+        <v>21</v>
+      </c>
+      <c r="E493" s="3">
+        <v>33</v>
+      </c>
+      <c r="F493" s="3">
+        <v>43</v>
+      </c>
+      <c r="G493" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="494" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A494" s="2">
+        <v>3037</v>
+      </c>
+      <c r="B494" s="3">
+        <v>2</v>
+      </c>
+      <c r="C494" s="3">
+        <v>11</v>
+      </c>
+      <c r="D494" s="3">
+        <v>22</v>
+      </c>
+      <c r="E494" s="3">
+        <v>30</v>
+      </c>
+      <c r="F494" s="3">
+        <v>51</v>
+      </c>
+      <c r="G494" s="3">
         <v>54</v>
       </c>
     </row>
@@ -11676,6 +11814,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -11843,15 +11990,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -11863,6 +12001,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9445F805-6E3A-4841-AEBD-CF7F6CDA924D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11882,14 +12028,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64615F65-CF13-4100-B135-FA0CB5E1C951}">
   <ds:schemaRefs>

--- a/LoteriasExcel/MegaSena_edt.xlsx
+++ b/LoteriasExcel/MegaSena_edt.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D54432-D0C7-4852-85D6-FF20C35EA65C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="997" yWindow="727" windowWidth="22036" windowHeight="10313" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="405" yWindow="248" windowWidth="25680" windowHeight="13455" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="MEGA SENA" sheetId="4" r:id="rId1"/>
@@ -109,13 +109,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11670,140 +11668,140 @@
       </c>
     </row>
     <row r="489" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A489" s="2">
+      <c r="A489">
         <v>3032</v>
       </c>
-      <c r="B489" s="3">
+      <c r="B489">
         <v>8</v>
       </c>
-      <c r="C489" s="3">
+      <c r="C489">
         <v>12</v>
       </c>
-      <c r="D489" s="3">
+      <c r="D489">
         <v>23</v>
       </c>
-      <c r="E489" s="3">
+      <c r="E489">
         <v>27</v>
       </c>
-      <c r="F489" s="3">
+      <c r="F489">
         <v>42</v>
       </c>
-      <c r="G489" s="3">
+      <c r="G489">
         <v>43</v>
       </c>
     </row>
     <row r="490" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A490" s="2">
+      <c r="A490">
         <v>3033</v>
       </c>
-      <c r="B490" s="3">
+      <c r="B490">
         <v>18</v>
       </c>
-      <c r="C490" s="3">
+      <c r="C490">
         <v>21</v>
       </c>
-      <c r="D490" s="3">
+      <c r="D490">
         <v>23</v>
       </c>
-      <c r="E490" s="3">
+      <c r="E490">
         <v>43</v>
       </c>
-      <c r="F490" s="3">
+      <c r="F490">
         <v>55</v>
       </c>
-      <c r="G490" s="3">
+      <c r="G490">
         <v>58</v>
       </c>
     </row>
     <row r="491" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A491" s="2">
+      <c r="A491">
         <v>3034</v>
       </c>
-      <c r="B491" s="3">
+      <c r="B491">
         <v>8</v>
       </c>
-      <c r="C491" s="3">
+      <c r="C491">
         <v>28</v>
       </c>
-      <c r="D491" s="3">
+      <c r="D491">
         <v>30</v>
       </c>
-      <c r="E491" s="3">
+      <c r="E491">
         <v>37</v>
       </c>
-      <c r="F491" s="3">
+      <c r="F491">
         <v>39</v>
       </c>
-      <c r="G491" s="3">
+      <c r="G491">
         <v>60</v>
       </c>
     </row>
     <row r="492" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A492" s="2">
+      <c r="A492">
         <v>3035</v>
       </c>
-      <c r="B492" s="3">
+      <c r="B492">
         <v>5</v>
       </c>
-      <c r="C492" s="3">
+      <c r="C492">
         <v>7</v>
       </c>
-      <c r="D492" s="3">
+      <c r="D492">
         <v>17</v>
       </c>
-      <c r="E492" s="3">
+      <c r="E492">
         <v>51</v>
       </c>
-      <c r="F492" s="3">
+      <c r="F492">
         <v>56</v>
       </c>
-      <c r="G492" s="3">
+      <c r="G492">
         <v>59</v>
       </c>
     </row>
     <row r="493" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A493" s="2">
+      <c r="A493">
         <v>3036</v>
       </c>
-      <c r="B493" s="3">
+      <c r="B493">
         <v>5</v>
       </c>
-      <c r="C493" s="3">
+      <c r="C493">
         <v>12</v>
       </c>
-      <c r="D493" s="3">
+      <c r="D493">
         <v>21</v>
       </c>
-      <c r="E493" s="3">
+      <c r="E493">
         <v>33</v>
       </c>
-      <c r="F493" s="3">
+      <c r="F493">
         <v>43</v>
       </c>
-      <c r="G493" s="3">
+      <c r="G493">
         <v>50</v>
       </c>
     </row>
     <row r="494" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A494" s="2">
+      <c r="A494">
         <v>3037</v>
       </c>
-      <c r="B494" s="3">
+      <c r="B494">
         <v>2</v>
       </c>
-      <c r="C494" s="3">
+      <c r="C494">
         <v>11</v>
       </c>
-      <c r="D494" s="3">
+      <c r="D494">
         <v>22</v>
       </c>
-      <c r="E494" s="3">
+      <c r="E494">
         <v>30</v>
       </c>
-      <c r="F494" s="3">
+      <c r="F494">
         <v>51</v>
       </c>
-      <c r="G494" s="3">
+      <c r="G494">
         <v>54</v>
       </c>
     </row>
@@ -11814,15 +11812,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -11990,6 +11979,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -12001,14 +11999,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9445F805-6E3A-4841-AEBD-CF7F6CDA924D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12028,6 +12018,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64615F65-CF13-4100-B135-FA0CB5E1C951}">
   <ds:schemaRefs>

--- a/LoteriasExcel/MegaSena_edt.xlsx
+++ b/LoteriasExcel/MegaSena_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D54432-D0C7-4852-85D6-FF20C35EA65C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E4FB3D4-92B5-4117-8CA7-CF4E8F9AB223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="405" yWindow="248" windowWidth="25680" windowHeight="13455" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="58365" yWindow="1125" windowWidth="25680" windowHeight="13455" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="MEGA SENA" sheetId="4" r:id="rId1"/>
@@ -434,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA4E33BD-754C-4CC3-9530-49E6C4C5E994}">
-  <dimension ref="A1:G494"/>
+  <dimension ref="A1:G495"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.06640625" customWidth="1"/>
@@ -11805,6 +11805,29 @@
         <v>54</v>
       </c>
     </row>
+    <row r="495" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A495">
+        <v>3038</v>
+      </c>
+      <c r="B495">
+        <v>30</v>
+      </c>
+      <c r="C495">
+        <v>35</v>
+      </c>
+      <c r="D495">
+        <v>38</v>
+      </c>
+      <c r="E495">
+        <v>39</v>
+      </c>
+      <c r="F495">
+        <v>46</v>
+      </c>
+      <c r="G495">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -11812,6 +11835,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -11979,15 +12011,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -11999,6 +12022,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9445F805-6E3A-4841-AEBD-CF7F6CDA924D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12018,14 +12049,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64615F65-CF13-4100-B135-FA0CB5E1C951}">
   <ds:schemaRefs>

--- a/LoteriasExcel/MegaSena_edt.xlsx
+++ b/LoteriasExcel/MegaSena_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E4FB3D4-92B5-4117-8CA7-CF4E8F9AB223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{948E920F-9FED-4E94-98FA-4EBF5216450C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="58365" yWindow="1125" windowWidth="25680" windowHeight="13455" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="58140" yWindow="780" windowWidth="13560" windowHeight="13455" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="MEGA SENA" sheetId="4" r:id="rId1"/>
@@ -434,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA4E33BD-754C-4CC3-9530-49E6C4C5E994}">
-  <dimension ref="A1:G495"/>
+  <dimension ref="A1:G496"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.06640625" customWidth="1"/>
@@ -11828,6 +11828,29 @@
         <v>50</v>
       </c>
     </row>
+    <row r="496" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A496">
+        <v>3039</v>
+      </c>
+      <c r="B496">
+        <v>14</v>
+      </c>
+      <c r="C496">
+        <v>16</v>
+      </c>
+      <c r="D496">
+        <v>21</v>
+      </c>
+      <c r="E496">
+        <v>39</v>
+      </c>
+      <c r="F496">
+        <v>53</v>
+      </c>
+      <c r="G496">
+        <v>58</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -11835,15 +11858,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -12011,6 +12025,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -12022,14 +12045,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9445F805-6E3A-4841-AEBD-CF7F6CDA924D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12049,6 +12064,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64615F65-CF13-4100-B135-FA0CB5E1C951}">
   <ds:schemaRefs>

--- a/LoteriasExcel/MegaSena_edt.xlsx
+++ b/LoteriasExcel/MegaSena_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{948E920F-9FED-4E94-98FA-4EBF5216450C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D602C750-14A8-4298-863A-FB2F037C3974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="58140" yWindow="780" windowWidth="13560" windowHeight="13455" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="2318" yWindow="525" windowWidth="25545" windowHeight="11603" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="MEGA SENA" sheetId="4" r:id="rId1"/>
@@ -434,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA4E33BD-754C-4CC3-9530-49E6C4C5E994}">
-  <dimension ref="A1:G496"/>
+  <dimension ref="A1:G497"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.06640625" customWidth="1"/>
@@ -11851,6 +11851,29 @@
         <v>58</v>
       </c>
     </row>
+    <row r="497" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A497">
+        <v>3040</v>
+      </c>
+      <c r="B497">
+        <v>3</v>
+      </c>
+      <c r="C497">
+        <v>16</v>
+      </c>
+      <c r="D497">
+        <v>24</v>
+      </c>
+      <c r="E497">
+        <v>30</v>
+      </c>
+      <c r="F497">
+        <v>49</v>
+      </c>
+      <c r="G497">
+        <v>54</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -11858,6 +11881,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -12025,15 +12057,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -12045,6 +12068,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9445F805-6E3A-4841-AEBD-CF7F6CDA924D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12064,14 +12095,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64615F65-CF13-4100-B135-FA0CB5E1C951}">
   <ds:schemaRefs>

--- a/LoteriasExcel/MegaSena_edt.xlsx
+++ b/LoteriasExcel/MegaSena_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D602C750-14A8-4298-863A-FB2F037C3974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE4C508-3C1D-4051-A22C-F2972A0AC9CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2318" yWindow="525" windowWidth="25545" windowHeight="11603" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="0" yWindow="1132" windowWidth="25545" windowHeight="10118" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="MEGA SENA" sheetId="4" r:id="rId1"/>
@@ -434,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA4E33BD-754C-4CC3-9530-49E6C4C5E994}">
-  <dimension ref="A1:G497"/>
+  <dimension ref="A1:G498"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.06640625" customWidth="1"/>
@@ -11874,6 +11874,29 @@
         <v>54</v>
       </c>
     </row>
+    <row r="498" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A498">
+        <v>3041</v>
+      </c>
+      <c r="B498">
+        <v>16</v>
+      </c>
+      <c r="C498">
+        <v>21</v>
+      </c>
+      <c r="D498">
+        <v>24</v>
+      </c>
+      <c r="E498">
+        <v>31</v>
+      </c>
+      <c r="F498">
+        <v>43</v>
+      </c>
+      <c r="G498">
+        <v>54</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -11881,15 +11904,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -12057,6 +12071,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -12068,14 +12091,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9445F805-6E3A-4841-AEBD-CF7F6CDA924D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12095,6 +12110,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64615F65-CF13-4100-B135-FA0CB5E1C951}">
   <ds:schemaRefs>

--- a/LoteriasExcel/MegaSena_edt.xlsx
+++ b/LoteriasExcel/MegaSena_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE4C508-3C1D-4051-A22C-F2972A0AC9CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9C79AE4-72D9-4A00-854F-24044E39AA36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1132" windowWidth="25545" windowHeight="10118" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="548" yWindow="232" windowWidth="23602" windowHeight="9421" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="MEGA SENA" sheetId="4" r:id="rId1"/>
@@ -434,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA4E33BD-754C-4CC3-9530-49E6C4C5E994}">
-  <dimension ref="A1:G498"/>
+  <dimension ref="A1:G502"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.06640625" customWidth="1"/>
@@ -11895,6 +11895,98 @@
       </c>
       <c r="G498">
         <v>54</v>
+      </c>
+    </row>
+    <row r="499" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A499">
+        <v>3042</v>
+      </c>
+      <c r="B499">
+        <v>2</v>
+      </c>
+      <c r="C499">
+        <v>5</v>
+      </c>
+      <c r="D499">
+        <v>10</v>
+      </c>
+      <c r="E499">
+        <v>35</v>
+      </c>
+      <c r="F499">
+        <v>40</v>
+      </c>
+      <c r="G499">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="500" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A500">
+        <v>3043</v>
+      </c>
+      <c r="B500">
+        <v>10</v>
+      </c>
+      <c r="C500">
+        <v>11</v>
+      </c>
+      <c r="D500">
+        <v>16</v>
+      </c>
+      <c r="E500">
+        <v>37</v>
+      </c>
+      <c r="F500">
+        <v>42</v>
+      </c>
+      <c r="G500">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="501" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A501">
+        <v>3044</v>
+      </c>
+      <c r="B501">
+        <v>4</v>
+      </c>
+      <c r="C501">
+        <v>15</v>
+      </c>
+      <c r="D501">
+        <v>17</v>
+      </c>
+      <c r="E501">
+        <v>40</v>
+      </c>
+      <c r="F501">
+        <v>55</v>
+      </c>
+      <c r="G501">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="502" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A502">
+        <v>3045</v>
+      </c>
+      <c r="B502">
+        <v>23</v>
+      </c>
+      <c r="C502">
+        <v>29</v>
+      </c>
+      <c r="D502">
+        <v>33</v>
+      </c>
+      <c r="E502">
+        <v>42</v>
+      </c>
+      <c r="F502">
+        <v>43</v>
+      </c>
+      <c r="G502">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/LoteriasExcel/MegaSena_edt.xlsx
+++ b/LoteriasExcel/MegaSena_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9C79AE4-72D9-4A00-854F-24044E39AA36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1951DA8-BDE0-4DAE-BBB1-3F2098FE408A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="548" yWindow="232" windowWidth="23602" windowHeight="9421" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="61530" yWindow="915" windowWidth="23610" windowHeight="9420" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="MEGA SENA" sheetId="4" r:id="rId1"/>
@@ -109,11 +109,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -434,7 +436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA4E33BD-754C-4CC3-9530-49E6C4C5E994}">
-  <dimension ref="A1:G502"/>
+  <dimension ref="A1:G503"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.06640625" customWidth="1"/>
@@ -11989,6 +11991,29 @@
         <v>57</v>
       </c>
     </row>
+    <row r="503" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A503" s="2">
+        <v>3046</v>
+      </c>
+      <c r="B503" s="3">
+        <v>16</v>
+      </c>
+      <c r="C503" s="3">
+        <v>23</v>
+      </c>
+      <c r="D503" s="3">
+        <v>24</v>
+      </c>
+      <c r="E503" s="3">
+        <v>33</v>
+      </c>
+      <c r="F503" s="3">
+        <v>36</v>
+      </c>
+      <c r="G503" s="3">
+        <v>52</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -11996,6 +12021,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -12163,15 +12197,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -12183,6 +12208,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9445F805-6E3A-4841-AEBD-CF7F6CDA924D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12202,14 +12235,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64615F65-CF13-4100-B135-FA0CB5E1C951}">
   <ds:schemaRefs>
